--- a/data/trans_bre/P1_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,1</t>
+          <t>-4,29; -0,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,87</t>
+          <t>0,31; 4,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 3,69</t>
+          <t>-3,45; 4,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 4,64</t>
+          <t>-4,49; 4,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-78,2; 11,78</t>
+          <t>-79,69; 6,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 607,29</t>
+          <t>0,94; 628,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 72,74</t>
+          <t>-39,89; 76,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-66,21; 263,43</t>
+          <t>-69,01; 309,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,55</t>
+          <t>-5,58; -0,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -2,56</t>
+          <t>-8,33; -2,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 0,08</t>
+          <t>-6,5; 0,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -2,79</t>
+          <t>-14,02; -3,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,72; -9,14</t>
+          <t>-66,35; -4,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,78; -31,35</t>
+          <t>-70,74; -28,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,86; 1,2</t>
+          <t>-51,58; 3,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,37; -22,68</t>
+          <t>-72,68; -23,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -1,88</t>
+          <t>-6,58; -1,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; -1,17</t>
+          <t>-5,27; -1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; -3,67</t>
+          <t>-9,44; -3,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,68; -6,21</t>
+          <t>-13,79; -6,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,83; -37,45</t>
+          <t>-82,5; -37,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,72; -29,97</t>
+          <t>-85,21; -26,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-73,37; -38,62</t>
+          <t>-74,37; -38,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,11; -48,8</t>
+          <t>-75,48; -46,44</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,54</t>
+          <t>-4,18; 1,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,07; -0,85</t>
+          <t>-6,68; -0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -3,87</t>
+          <t>-10,67; -4,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 0,76</t>
+          <t>-15,05; -0,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,62; 35,68</t>
+          <t>-54,55; 41,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,31; -10,1</t>
+          <t>-64,76; -7,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,62; -34,13</t>
+          <t>-71,65; -35,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,63; 7,23</t>
+          <t>-70,27; -2,18</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,33</t>
+          <t>-1,92; 5,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,54</t>
+          <t>-2,36; 5,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 8,55</t>
+          <t>-1,13; 8,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 1,13</t>
+          <t>-6,88; 0,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 106,02</t>
+          <t>-23,48; 113,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 114,49</t>
+          <t>-28,5; 92,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 90,56</t>
+          <t>-7,89; 90,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 6,43</t>
+          <t>-30,39; 5,03</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,65; 17,47</t>
+          <t>6,74; 17,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 17,52</t>
+          <t>5,72; 17,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,98</t>
+          <t>2,26; 14,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 12,62</t>
+          <t>-14,22; 12,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56,54; 259,16</t>
+          <t>54,6; 254,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,95; 195,62</t>
+          <t>33,3; 185,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,56; 115,49</t>
+          <t>8,83; 111,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,42; 59,91</t>
+          <t>-58,1; 61,08</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 21,37</t>
+          <t>6,25; 21,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 21,82</t>
+          <t>7,67; 22,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 21,46</t>
+          <t>5,8; 21,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,49; 30,06</t>
+          <t>18,63; 30,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,83; 132,83</t>
+          <t>24,83; 128,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,15; 117,17</t>
+          <t>27,04; 120,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,38; 94,96</t>
+          <t>18,27; 91,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,36; 108,05</t>
+          <t>52,81; 109,5</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,76</t>
+          <t>0,03; 2,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,96</t>
+          <t>0,26; 3,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,34</t>
+          <t>-1,05; 2,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,69</t>
+          <t>-3,66; 2,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 42,4</t>
+          <t>0,63; 42,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 38,39</t>
+          <t>3,2; 41,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 20,38</t>
+          <t>-7,64; 20,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 18,47</t>
+          <t>-20,14; 19,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>-1,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>-28,56%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; -0,1</t>
+          <t>-4,38; -0,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,94</t>
+          <t>0,37; 4,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,11</t>
+          <t>-3,51; 4,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 4,91</t>
+          <t>-6,85; 2,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-79,69; 6,74</t>
+          <t>-80,02; 3,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 628,54</t>
+          <t>1,04; 636,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 76,12</t>
+          <t>-38,75; 87,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 309,7</t>
+          <t>-69,08; 99,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,17</t>
+          <t>-7,12</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-51,13%</t>
+          <t>-44,78%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -0,43</t>
+          <t>-5,61; -0,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,33; -2,5</t>
+          <t>-8,49; -2,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,16</t>
+          <t>-6,67; -0,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,02; -3,13</t>
+          <t>-12,39; -1,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,35; -4,12</t>
+          <t>-68,19; -12,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,74; -28,67</t>
+          <t>-70,7; -28,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 3,83</t>
+          <t>-53,34; -0,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,68; -23,95</t>
+          <t>-63,67; -14,39</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-9,85</t>
+          <t>-10,13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-63,62%</t>
+          <t>-63,71%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; -1,89</t>
+          <t>-6,7; -2,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -1,19</t>
+          <t>-5,01; -1,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,44; -3,55</t>
+          <t>-9,43; -3,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -6,41</t>
+          <t>-13,8; -6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,5; -37,96</t>
+          <t>-83,27; -39,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-85,21; -26,61</t>
+          <t>-84,55; -28,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,37; -38,53</t>
+          <t>-73,36; -37,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,48; -46,44</t>
+          <t>-75,4; -49,69</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-13,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-53,69%</t>
+          <t>-64,13%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 1,85</t>
+          <t>-4,27; 1,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,68; -0,79</t>
+          <t>-7,08; -0,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -4,17</t>
+          <t>-10,63; -3,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -0,11</t>
+          <t>-16,77; -9,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,55; 41,23</t>
+          <t>-54,72; 45,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,76; -7,53</t>
+          <t>-66,86; -12,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,65; -35,43</t>
+          <t>-71,78; -33,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,27; -2,18</t>
+          <t>-71,58; -52,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,85</t>
+          <t>-3,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-14,34%</t>
+          <t>-15,69%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,85</t>
+          <t>-2,11; 5,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 5,19</t>
+          <t>-2,24; 5,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 8,28</t>
+          <t>-0,99; 8,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 0,94</t>
+          <t>-7,28; 0,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 113,4</t>
+          <t>-23,62; 119,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 92,33</t>
+          <t>-24,59; 106,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 90,19</t>
+          <t>-8,46; 87,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 5,03</t>
+          <t>-32,05; 5,42</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>11,13</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 17,61</t>
+          <t>7,07; 18,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,72; 17,43</t>
+          <t>4,92; 17,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 14,4</t>
+          <t>2,69; 14,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 12,68</t>
+          <t>6,27; 15,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54,6; 254,42</t>
+          <t>57,21; 266,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,3; 185,81</t>
+          <t>31,09; 188,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,83; 111,98</t>
+          <t>14,3; 114,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 61,08</t>
+          <t>24,86; 82,98</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 21,17</t>
+          <t>6,05; 21,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,67; 22,03</t>
+          <t>6,44; 22,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 21,04</t>
+          <t>6,59; 21,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,63; 30,02</t>
+          <t>19,03; 30,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,83; 128,96</t>
+          <t>21,22; 129,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,04; 120,63</t>
+          <t>22,25; 118,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,27; 91,85</t>
+          <t>22,23; 96,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>52,81; 109,5</t>
+          <t>55,77; 113,33</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-3,08%</t>
+          <t>-4,51%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,73</t>
+          <t>0,07; 2,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,11</t>
+          <t>0,1; 2,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,43</t>
+          <t>-0,88; 2,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,82</t>
+          <t>-2,5; 0,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 42,5</t>
+          <t>0,89; 44,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,2; 41,48</t>
+          <t>1,07; 39,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 20,78</t>
+          <t>-6,68; 20,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 19,67</t>
+          <t>-13,0; 4,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
